--- a/data/trans_dic/P62-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P62-Habitat-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que percibe algun tipo de pensión</t>
+          <t>Población que percibe algun tipo de pensión (tasa de respuesta: 99,15%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>50,48; 61,48</t>
+          <t>50,52; 61,27</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>44,48; 54,2</t>
+          <t>44,54; 54,37</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>39,91; 49,46</t>
+          <t>39,87; 49,48</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>53,03; 66,02</t>
+          <t>52,92; 66,42</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>20,22; 27,61</t>
+          <t>20,18; 27,45</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>27,51; 36,11</t>
+          <t>27,78; 35,98</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>25,84; 34,11</t>
+          <t>25,94; 34,83</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>37,52; 44,91</t>
+          <t>37,48; 44,46</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>32,56; 38,9</t>
+          <t>32,45; 39,1</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>36,51; 43,02</t>
+          <t>36,43; 42,89</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>33,22; 39,72</t>
+          <t>33,4; 39,86</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>45,48; 52,31</t>
+          <t>45,13; 52,26</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>51,07; 61,0</t>
+          <t>51,01; 61,14</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>37,03; 45,29</t>
+          <t>37,15; 44,77</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>40,2; 47,95</t>
+          <t>39,82; 48,03</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>46,06; 57,42</t>
+          <t>45,92; 57,67</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>18,7; 25,32</t>
+          <t>18,82; 25,16</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>24,8; 31,35</t>
+          <t>24,51; 31,29</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>23,58; 30,27</t>
+          <t>23,59; 30,43</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>30,11; 36,73</t>
+          <t>30,59; 36,82</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>31,66; 37,45</t>
+          <t>31,4; 37,21</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>30,96; 36,5</t>
+          <t>31,17; 36,36</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>31,73; 37,29</t>
+          <t>32,06; 37,25</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>37,88; 43,99</t>
+          <t>37,95; 44,07</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>51,43; 63,66</t>
+          <t>51,31; 63,63</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>34,0; 43,97</t>
+          <t>34,03; 44,07</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>41,54; 51,55</t>
+          <t>41,62; 51,57</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>51,51; 65,3</t>
+          <t>51,39; 64,18</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>22,05; 30,33</t>
+          <t>22,25; 30,09</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>22,72; 30,8</t>
+          <t>22,84; 30,49</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>22,73; 31,48</t>
+          <t>23,61; 32,16</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>34,54; 79,9</t>
+          <t>34,85; 85,09</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>34,39; 40,96</t>
+          <t>33,93; 41,02</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>29,27; 35,22</t>
+          <t>28,85; 34,88</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>32,72; 39,41</t>
+          <t>32,66; 39,1</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>44,91; 77,59</t>
+          <t>44,88; 77,1</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>44,87; 54,4</t>
+          <t>44,26; 54,23</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>42,77; 51,61</t>
+          <t>42,82; 51,97</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>45,77; 54,47</t>
+          <t>45,76; 54,25</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>43,75; 54,81</t>
+          <t>44,08; 54,2</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>23,91; 31,03</t>
+          <t>23,86; 30,76</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>26,8; 33,8</t>
+          <t>27,33; 33,98</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>31,95; 39,59</t>
+          <t>31,87; 39,53</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>36,0; 42,66</t>
+          <t>36,1; 43,04</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>32,64; 38,55</t>
+          <t>32,8; 38,67</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>34,69; 40,46</t>
+          <t>34,7; 40,14</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>38,99; 44,61</t>
+          <t>39,1; 44,88</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>40,79; 46,48</t>
+          <t>40,57; 46,37</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>51,84; 57,23</t>
+          <t>51,94; 57,15</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>41,5; 46,28</t>
+          <t>41,76; 46,19</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>44,11; 48,56</t>
+          <t>44,08; 48,6</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>51,19; 57,15</t>
+          <t>51,16; 57,44</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>22,8; 26,4</t>
+          <t>22,96; 26,44</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>27,18; 30,79</t>
+          <t>27,43; 30,93</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>28,31; 32,25</t>
+          <t>28,23; 32,08</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>36,79; 62,01</t>
+          <t>36,89; 59,56</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>34,06; 37,23</t>
+          <t>34,13; 37,28</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>34,16; 37,13</t>
+          <t>34,15; 36,95</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>35,94; 38,83</t>
+          <t>35,76; 38,64</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>44,09; 59,01</t>
+          <t>44,13; 58,3</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que percibe algun tipo de pensión</t>
+          <t>Población que percibe algun tipo de pensión (tasa de respuesta: 99,15%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>154013; 187581</t>
+          <t>154135; 186933</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>191495; 233314</t>
+          <t>191740; 234056</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>169843; 210487</t>
+          <t>169689; 210594</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>159609; 198689</t>
+          <t>159285; 199889</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>107193; 146372</t>
+          <t>106984; 145496</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>143565; 188492</t>
+          <t>144978; 187778</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>128700; 169890</t>
+          <t>129193; 173450</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>155545; 186177</t>
+          <t>155383; 184295</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>271926; 324874</t>
+          <t>271053; 326583</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>347693; 409777</t>
+          <t>346980; 408501</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>306849; 366904</t>
+          <t>308476; 368143</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>325393; 374290</t>
+          <t>322924; 373928</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>204677; 244465</t>
+          <t>204448; 245049</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>222923; 272659</t>
+          <t>223620; 269545</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>241909; 288572</t>
+          <t>239664; 289040</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>176088; 219526</t>
+          <t>175580; 220510</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>130997; 177415</t>
+          <t>131886; 176263</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>186607; 235893</t>
+          <t>184471; 235443</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>177724; 228152</t>
+          <t>177828; 229344</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>165927; 202427</t>
+          <t>168609; 202952</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>348766; 412530</t>
+          <t>345850; 409874</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>419335; 494395</t>
+          <t>422272; 492486</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>430060; 505470</t>
+          <t>434512; 504901</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>353565; 410652</t>
+          <t>354232; 411387</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>138722; 171705</t>
+          <t>138386; 171611</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>146960; 190094</t>
+          <t>147115; 190513</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>161958; 201000</t>
+          <t>162280; 201072</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>177529; 225080</t>
+          <t>177116; 221212</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>102800; 141388</t>
+          <t>103719; 140297</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>126977; 172145</t>
+          <t>127636; 170408</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>114827; 159059</t>
+          <t>119261; 162472</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>209446; 484548</t>
+          <t>211349; 516032</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>253043; 301389</t>
+          <t>249713; 301896</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>290151; 349073</t>
+          <t>285916; 345717</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>292860; 352745</t>
+          <t>292315; 350001</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>427172; 737949</t>
+          <t>426820; 733265</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>172207; 208772</t>
+          <t>169846; 208110</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>220957; 266636</t>
+          <t>221206; 268487</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>242085; 288113</t>
+          <t>242027; 286957</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>197975; 248026</t>
+          <t>199465; 245276</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>155324; 201530</t>
+          <t>155002; 199774</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>198368; 250195</t>
+          <t>202294; 251498</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>224103; 277667</t>
+          <t>223513; 277261</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>218184; 258538</t>
+          <t>218764; 260804</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>337262; 398298</t>
+          <t>338961; 399616</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>435918; 508495</t>
+          <t>436100; 504410</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>479725; 548847</t>
+          <t>481004; 552153</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>431759; 491978</t>
+          <t>429419; 490892</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>704703; 777999</t>
+          <t>706023; 776905</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>822352; 917084</t>
+          <t>827419; 915256</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>858465; 945068</t>
+          <t>857980; 945922</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>757945; 846187</t>
+          <t>757511; 850378</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>535011; 619576</t>
+          <t>538793; 620420</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>699546; 792414</t>
+          <t>705813; 795939</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>695881; 792794</t>
+          <t>693930; 788550</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>801281; 1350692</t>
+          <t>803430; 1297233</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>1262052; 1379693</t>
+          <t>1264825; 1381379</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1556186; 1691213</t>
+          <t>1555651; 1682935</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>1583199; 1710332</t>
+          <t>1575264; 1701824</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>1612998; 2158940</t>
+          <t>1614534; 2133061</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P62-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P62-Habitat-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>59,8%</t>
+          <t>61,26%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>41,03%</t>
+          <t>40,25%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>48,92%</t>
+          <t>48,99%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>50,52; 61,27</t>
+          <t>50,58; 61,58</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>44,54; 54,37</t>
+          <t>44,57; 54,22</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>39,87; 49,48</t>
+          <t>39,59; 49,68</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>52,92; 66,42</t>
+          <t>54,95; 67,02</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>20,18; 27,45</t>
+          <t>20,05; 27,45</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>27,78; 35,98</t>
+          <t>27,56; 35,54</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>25,94; 34,83</t>
+          <t>25,61; 34,03</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>37,48; 44,46</t>
+          <t>36,66; 43,8</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>32,45; 39,1</t>
+          <t>32,54; 39,23</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>36,43; 42,89</t>
+          <t>36,68; 43,43</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>33,4; 39,86</t>
+          <t>33,66; 40,05</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>45,13; 52,26</t>
+          <t>45,37; 52,09</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>51,83%</t>
+          <t>52,77%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>33,53%</t>
+          <t>33,25%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>41,02%</t>
+          <t>41,12%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>51,01; 61,14</t>
+          <t>51,12; 61,28</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>37,15; 44,77</t>
+          <t>36,86; 45,09</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>39,82; 48,03</t>
+          <t>39,89; 48,13</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>45,92; 57,67</t>
+          <t>47,68; 58,79</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>18,82; 25,16</t>
+          <t>18,99; 25,25</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>24,51; 31,29</t>
+          <t>24,25; 31,2</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>23,59; 30,43</t>
+          <t>23,55; 30,39</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>30,59; 36,82</t>
+          <t>30,08; 36,86</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>31,4; 37,21</t>
+          <t>31,74; 37,36</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>31,17; 36,36</t>
+          <t>31,07; 36,29</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>32,06; 37,25</t>
+          <t>31,78; 37,44</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>37,95; 44,07</t>
+          <t>38,09; 43,9</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>58,28%</t>
+          <t>59,78%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>57,67%</t>
+          <t>35,01%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>57,89%</t>
+          <t>46,06%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>51,31; 63,63</t>
+          <t>51,51; 63,47</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>34,03; 44,07</t>
+          <t>34,26; 44,24</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>41,62; 51,57</t>
+          <t>40,82; 51,51</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>51,39; 64,18</t>
+          <t>53,49; 66,76</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>22,25; 30,09</t>
+          <t>22,1; 30,18</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>22,84; 30,49</t>
+          <t>22,79; 30,58</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>23,61; 32,16</t>
+          <t>23,21; 31,77</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>34,85; 85,09</t>
+          <t>31,57; 38,72</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>33,93; 41,02</t>
+          <t>33,58; 40,71</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>28,85; 34,88</t>
+          <t>29,07; 35,27</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>32,66; 39,1</t>
+          <t>32,72; 39,19</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>44,88; 77,1</t>
+          <t>42,37; 49,12</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>49,16%</t>
+          <t>49,32%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>39,33%</t>
+          <t>39,2%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>43,53%</t>
+          <t>43,39%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>44,26; 54,23</t>
+          <t>44,83; 54,99</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>42,82; 51,97</t>
+          <t>42,94; 51,69</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>45,76; 54,25</t>
+          <t>46,0; 54,58</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>44,08; 54,2</t>
+          <t>43,77; 53,87</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>23,86; 30,76</t>
+          <t>23,87; 30,61</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>27,33; 33,98</t>
+          <t>27,1; 33,84</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>31,87; 39,53</t>
+          <t>31,99; 39,63</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>36,1; 43,04</t>
+          <t>35,54; 42,17</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>32,8; 38,67</t>
+          <t>32,51; 38,5</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>34,7; 40,14</t>
+          <t>34,81; 40,58</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>39,1; 44,88</t>
+          <t>39,21; 44,81</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>40,57; 46,37</t>
+          <t>40,54; 46,32</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>54,13%</t>
+          <t>55,14%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>43,29%</t>
+          <t>36,85%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>47,68%</t>
+          <t>44,51%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>51,94; 57,15</t>
+          <t>51,86; 57,12</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>41,76; 46,19</t>
+          <t>41,74; 46,27</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>44,08; 48,6</t>
+          <t>43,94; 48,4</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>51,16; 57,44</t>
+          <t>52,16; 57,79</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>22,96; 26,44</t>
+          <t>22,86; 26,49</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>27,43; 30,93</t>
+          <t>27,22; 30,93</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>28,23; 32,08</t>
+          <t>28,2; 32,06</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>36,89; 59,56</t>
+          <t>35,12; 38,54</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>34,13; 37,28</t>
+          <t>34,19; 37,31</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>34,15; 36,95</t>
+          <t>34,19; 37,12</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>35,76; 38,64</t>
+          <t>35,92; 38,72</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>44,13; 58,3</t>
+          <t>42,86; 46,05</t>
         </is>
       </c>
     </row>
@@ -1592,7 +1592,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>179964</t>
+          <t>196624</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1612,7 +1612,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>170085</t>
+          <t>181294</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>350049</t>
+          <t>377918</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>154135; 186933</t>
+          <t>154315; 187864</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>191740; 234056</t>
+          <t>191889; 233425</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>169689; 210594</t>
+          <t>168505; 211428</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>159285; 199889</t>
+          <t>176388; 215117</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>106984; 145496</t>
+          <t>106274; 145512</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>144978; 187778</t>
+          <t>143848; 185509</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>129193; 173450</t>
+          <t>127555; 169505</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>155383; 184295</t>
+          <t>165107; 197263</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>271053; 326583</t>
+          <t>271809; 327641</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>346980; 408501</t>
+          <t>349390; 413606</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>308476; 368143</t>
+          <t>310935; 369959</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>322924; 373928</t>
+          <t>349987; 401795</t>
         </is>
       </c>
     </row>
@@ -1800,7 +1800,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>198172</t>
+          <t>219541</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1820,7 +1820,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>184788</t>
+          <t>204828</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>382961</t>
+          <t>424370</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>204448; 245049</t>
+          <t>204896; 245612</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>223620; 269545</t>
+          <t>221903; 271473</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>239664; 289040</t>
+          <t>240069; 289630</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>175580; 220510</t>
+          <t>198388; 244607</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>131886; 176263</t>
+          <t>133072; 176929</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>184471; 235443</t>
+          <t>182485; 234827</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>177828; 229344</t>
+          <t>177509; 229062</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>168609; 202952</t>
+          <t>185294; 227058</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>345850; 409874</t>
+          <t>349596; 411549</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>422272; 492486</t>
+          <t>420931; 491594</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>434512; 504901</t>
+          <t>430767; 507483</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>354232; 411387</t>
+          <t>393108; 453118</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>200866</t>
+          <t>226453</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2028,7 +2028,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>349752</t>
+          <t>164569</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>550618</t>
+          <t>391022</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>138386; 171611</t>
+          <t>138913; 171177</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>147115; 190513</t>
+          <t>148117; 191241</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>162280; 201072</t>
+          <t>159179; 200849</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>177116; 221212</t>
+          <t>202605; 252882</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>103719; 140297</t>
+          <t>103023; 140677</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>127636; 170408</t>
+          <t>127361; 170883</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>119261; 162472</t>
+          <t>117274; 160496</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>211349; 516032</t>
+          <t>148401; 182019</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>249713; 301896</t>
+          <t>247134; 299565</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>285916; 345717</t>
+          <t>288160; 349612</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>292315; 350001</t>
+          <t>292930; 350787</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>426820; 733265</t>
+          <t>359695; 416995</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>222468</t>
+          <t>231831</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>238337</t>
+          <t>260073</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>460805</t>
+          <t>491905</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>169846; 208110</t>
+          <t>172062; 211033</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>221206; 268487</t>
+          <t>221838; 267049</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>242027; 286957</t>
+          <t>243295; 288688</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>199465; 245276</t>
+          <t>205745; 253230</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>155002; 199774</t>
+          <t>155058; 198853</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>202294; 251498</t>
+          <t>200581; 250510</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>223513; 277261</t>
+          <t>224368; 277967</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>218764; 260804</t>
+          <t>235830; 279817</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>338961; 399616</t>
+          <t>335909; 397792</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>436100; 504410</t>
+          <t>437428; 509968</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>481004; 552153</t>
+          <t>482412; 551302</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>429419; 490892</t>
+          <t>459556; 525129</t>
         </is>
       </c>
     </row>
@@ -2424,7 +2424,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>801470</t>
+          <t>874450</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2444,7 +2444,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>942962</t>
+          <t>810764</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>1744432</t>
+          <t>1685213</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>706023; 776905</t>
+          <t>704978; 776480</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>827419; 915256</t>
+          <t>827071; 916749</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>857980; 945922</t>
+          <t>855290; 942040</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>757511; 850378</t>
+          <t>827195; 916420</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>538793; 620420</t>
+          <t>536304; 621544</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>705813; 795939</t>
+          <t>700539; 796120</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>693930; 788550</t>
+          <t>693138; 788114</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>803430; 1297233</t>
+          <t>772622; 847928</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>1264825; 1381379</t>
+          <t>1267016; 1382544</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1555651; 1682935</t>
+          <t>1557149; 1690707</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>1575264; 1701824</t>
+          <t>1582330; 1705488</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>1614534; 2133061</t>
+          <t>1622520; 1743348</t>
         </is>
       </c>
     </row>
